--- a/data/Boltonia_LCMS_20240624.xlsx
+++ b/data/Boltonia_LCMS_20240624.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27813"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_B74F6E9A36111B2D0122A6351AB4730B9B153101" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gowustl-my.sharepoint.com/personal/wen-hsi_kuo_wustl_edu/Documents/MOBOT/MOBOT_Boltonia/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_B74F6E9A36111B2D0122A6351AB4730B9B153101" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B0C5F81-C444-174F-AE9E-422EC5FFD590}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="45" windowWidth="18195" windowHeight="7995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="760" windowWidth="30600" windowHeight="16120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AK$1</definedName>
   </definedNames>
-  <calcPr calcId="145621" fullCalcOnLoad="1"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1525,7 +1530,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1874,12 +1879,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK127"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="37" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="14.1640625" customWidth="1"/>
+    <col min="2" max="2" width="23.1640625" customWidth="1"/>
+    <col min="3" max="31" width="14.1640625" customWidth="1"/>
+    <col min="32" max="32" width="95.33203125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="40.1640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="37" width="14.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1992,7 +2002,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1086807</v>
       </c>
@@ -2069,7 +2079,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1086808</v>
       </c>
@@ -2149,7 +2159,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1081254</v>
       </c>
@@ -2223,7 +2233,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1081255</v>
       </c>
@@ -2294,7 +2304,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:37">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1098202</v>
       </c>
@@ -2344,7 +2354,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:37">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1102620</v>
       </c>
@@ -2391,7 +2401,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:37">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1109428</v>
       </c>
@@ -2471,7 +2481,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:37">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1109429</v>
       </c>
@@ -2551,7 +2561,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:37">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1118519</v>
       </c>
@@ -2628,7 +2638,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:37">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1118525</v>
       </c>
@@ -2702,7 +2712,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:37">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1118526</v>
       </c>
@@ -2776,7 +2786,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:37">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>1118527</v>
       </c>
@@ -2850,7 +2860,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:37">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>1118528</v>
       </c>
@@ -2924,7 +2934,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:37">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1118529</v>
       </c>
@@ -2998,7 +3008,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:37">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>1118530</v>
       </c>
@@ -3075,7 +3085,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:35">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1118531</v>
       </c>
@@ -3152,7 +3162,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:35">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>1118532</v>
       </c>
@@ -3229,7 +3239,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:35">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>1118520</v>
       </c>
@@ -3306,7 +3316,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:35">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1118521</v>
       </c>
@@ -3383,7 +3393,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:35">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>1118522</v>
       </c>
@@ -3460,7 +3470,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:35">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>1118523</v>
       </c>
@@ -3537,7 +3547,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:35">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>1118524</v>
       </c>
@@ -3614,7 +3624,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:35">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>1118533</v>
       </c>
@@ -3685,7 +3695,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:35">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>1118534</v>
       </c>
@@ -3756,7 +3766,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:35">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>1122941</v>
       </c>
@@ -3836,7 +3846,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:35">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>1122942</v>
       </c>
@@ -3913,7 +3923,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:35">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>1122943</v>
       </c>
@@ -3990,7 +4000,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:35">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>1122944</v>
       </c>
@@ -4067,7 +4077,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:35">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>1120390</v>
       </c>
@@ -4150,7 +4160,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:35">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>1120391</v>
       </c>
@@ -4233,7 +4243,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:35">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>1120392</v>
       </c>
@@ -4316,7 +4326,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="1:35">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>1120393</v>
       </c>
@@ -4402,7 +4412,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:35">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>1120394</v>
       </c>
@@ -4485,7 +4495,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:35">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>1152628</v>
       </c>
@@ -4532,7 +4542,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:35">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>1179998</v>
       </c>
@@ -4612,7 +4622,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:35">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>1179999</v>
       </c>
@@ -4695,7 +4705,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="1:35">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>1180000</v>
       </c>
@@ -4778,7 +4788,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:35">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>1180001</v>
       </c>
@@ -4855,7 +4865,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="1:35">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>1180002</v>
       </c>
@@ -4938,7 +4948,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="41" spans="1:35">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>1180003</v>
       </c>
@@ -5021,7 +5031,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="1:35">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>1180004</v>
       </c>
@@ -5095,7 +5105,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="43" spans="1:35">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>1180005</v>
       </c>
@@ -5169,7 +5179,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="44" spans="1:35">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>1180006</v>
       </c>
@@ -5243,7 +5253,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="1:35">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>1180007</v>
       </c>
@@ -5317,7 +5327,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="1:35">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>1180008</v>
       </c>
@@ -5391,7 +5401,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="1:35">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>1180009</v>
       </c>
@@ -5465,7 +5475,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:35">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>1180010</v>
       </c>
@@ -5539,7 +5549,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:35">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>1180011</v>
       </c>
@@ -5622,7 +5632,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="50" spans="1:35">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>1180012</v>
       </c>
@@ -5705,7 +5715,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="1:35">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>1180013</v>
       </c>
@@ -5779,7 +5789,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="52" spans="1:35">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>1180014</v>
       </c>
@@ -5862,7 +5872,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:35">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>1180015</v>
       </c>
@@ -5945,7 +5955,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:35">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>1180016</v>
       </c>
@@ -6028,7 +6038,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="1:35">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>1180017</v>
       </c>
@@ -6105,7 +6115,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="56" spans="1:35">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>1180018</v>
       </c>
@@ -6188,7 +6198,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="57" spans="1:35">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>1180019</v>
       </c>
@@ -6265,7 +6275,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="58" spans="1:35">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>1180020</v>
       </c>
@@ -6348,7 +6358,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:35">
+    <row r="59" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>1180021</v>
       </c>
@@ -6431,7 +6441,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:35">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>1180022</v>
       </c>
@@ -6514,7 +6524,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="61" spans="1:35">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>1180023</v>
       </c>
@@ -6597,7 +6607,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="62" spans="1:35">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>1180024</v>
       </c>
@@ -6680,7 +6690,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="63" spans="1:35">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>1180025</v>
       </c>
@@ -6757,7 +6767,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="64" spans="1:35">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>1180026</v>
       </c>
@@ -6834,7 +6844,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="65" spans="1:35">
+    <row r="65" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>1180027</v>
       </c>
@@ -6917,7 +6927,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="66" spans="1:35">
+    <row r="66" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>1180028</v>
       </c>
@@ -7000,7 +7010,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="1:35">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>1180029</v>
       </c>
@@ -7083,7 +7093,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="68" spans="1:35">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>1180030</v>
       </c>
@@ -7166,7 +7176,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="69" spans="1:35">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>1180031</v>
       </c>
@@ -7249,7 +7259,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="70" spans="1:35">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>1180032</v>
       </c>
@@ -7332,7 +7342,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="71" spans="1:35">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>1180033</v>
       </c>
@@ -7415,7 +7425,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="72" spans="1:35">
+    <row r="72" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>1180034</v>
       </c>
@@ -7498,7 +7508,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="73" spans="1:35">
+    <row r="73" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>1180035</v>
       </c>
@@ -7575,7 +7585,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="74" spans="1:35">
+    <row r="74" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>1180036</v>
       </c>
@@ -7658,7 +7668,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="75" spans="1:35">
+    <row r="75" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>1180037</v>
       </c>
@@ -7735,7 +7745,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="76" spans="1:35">
+    <row r="76" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>1180038</v>
       </c>
@@ -7812,7 +7822,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="77" spans="1:35">
+    <row r="77" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>1180039</v>
       </c>
@@ -7895,7 +7905,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="78" spans="1:35">
+    <row r="78" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>1180040</v>
       </c>
@@ -7978,7 +7988,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="79" spans="1:35">
+    <row r="79" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>1180041</v>
       </c>
@@ -8067,7 +8077,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="80" spans="1:35">
+    <row r="80" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>1180042</v>
       </c>
@@ -8150,7 +8160,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="81" spans="1:35">
+    <row r="81" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>1180043</v>
       </c>
@@ -8233,7 +8243,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="82" spans="1:35">
+    <row r="82" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>1180044</v>
       </c>
@@ -8316,7 +8326,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="83" spans="1:35">
+    <row r="83" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>1180045</v>
       </c>
@@ -8399,7 +8409,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="84" spans="1:35">
+    <row r="84" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>1180046</v>
       </c>
@@ -8482,7 +8492,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="85" spans="1:35">
+    <row r="85" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>1180047</v>
       </c>
@@ -8559,7 +8569,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="86" spans="1:35">
+    <row r="86" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>1180048</v>
       </c>
@@ -8642,7 +8652,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="87" spans="1:35">
+    <row r="87" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>1180049</v>
       </c>
@@ -8725,7 +8735,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="88" spans="1:35">
+    <row r="88" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>1180050</v>
       </c>
@@ -8802,7 +8812,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="89" spans="1:35">
+    <row r="89" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>1180051</v>
       </c>
@@ -8879,7 +8889,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="90" spans="1:35">
+    <row r="90" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>1180052</v>
       </c>
@@ -8962,7 +8972,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="91" spans="1:35">
+    <row r="91" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>1180053</v>
       </c>
@@ -9048,7 +9058,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="92" spans="1:35">
+    <row r="92" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>1180054</v>
       </c>
@@ -9125,7 +9135,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="93" spans="1:35">
+    <row r="93" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>1180055</v>
       </c>
@@ -9208,7 +9218,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="94" spans="1:35">
+    <row r="94" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>1180056</v>
       </c>
@@ -9291,7 +9301,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="95" spans="1:35">
+    <row r="95" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>1180057</v>
       </c>
@@ -9374,7 +9384,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="96" spans="1:35">
+    <row r="96" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>1180058</v>
       </c>
@@ -9457,7 +9467,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="97" spans="1:35">
+    <row r="97" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>1180059</v>
       </c>
@@ -9540,7 +9550,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="98" spans="1:35">
+    <row r="98" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>1180060</v>
       </c>
@@ -9626,7 +9636,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="99" spans="1:35">
+    <row r="99" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>1180061</v>
       </c>
@@ -9703,7 +9713,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="100" spans="1:35">
+    <row r="100" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>1180062</v>
       </c>
@@ -9783,7 +9793,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="101" spans="1:35">
+    <row r="101" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>1180063</v>
       </c>
@@ -9869,7 +9879,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="102" spans="1:35">
+    <row r="102" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>1180064</v>
       </c>
@@ -9946,7 +9956,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="103" spans="1:35">
+    <row r="103" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>1180065</v>
       </c>
@@ -10029,7 +10039,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="104" spans="1:35">
+    <row r="104" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>1180066</v>
       </c>
@@ -10112,7 +10122,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="105" spans="1:35">
+    <row r="105" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>1180067</v>
       </c>
@@ -10195,7 +10205,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="106" spans="1:35">
+    <row r="106" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>1180068</v>
       </c>
@@ -10272,7 +10282,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="107" spans="1:35">
+    <row r="107" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>1180069</v>
       </c>
@@ -10355,7 +10365,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="108" spans="1:35">
+    <row r="108" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>1180070</v>
       </c>
@@ -10438,7 +10448,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="109" spans="1:35">
+    <row r="109" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>1180072</v>
       </c>
@@ -10521,7 +10531,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="110" spans="1:35">
+    <row r="110" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>1180073</v>
       </c>
@@ -10598,7 +10608,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="111" spans="1:35">
+    <row r="111" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>1180074</v>
       </c>
@@ -10681,7 +10691,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="112" spans="1:35">
+    <row r="112" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>1180075</v>
       </c>
@@ -10758,7 +10768,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="113" spans="1:35">
+    <row r="113" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>1180076</v>
       </c>
@@ -10844,7 +10854,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="114" spans="1:35">
+    <row r="114" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>1180077</v>
       </c>
@@ -10921,7 +10931,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="115" spans="1:35">
+    <row r="115" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>1180078</v>
       </c>
@@ -11004,7 +11014,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="116" spans="1:35">
+    <row r="116" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>1180079</v>
       </c>
@@ -11081,7 +11091,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="117" spans="1:35">
+    <row r="117" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>1180080</v>
       </c>
@@ -11158,7 +11168,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="118" spans="1:35">
+    <row r="118" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>1180081</v>
       </c>
@@ -11235,7 +11245,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="119" spans="1:35">
+    <row r="119" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>1180082</v>
       </c>
@@ -11312,7 +11322,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="120" spans="1:35">
+    <row r="120" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>1180083</v>
       </c>
@@ -11395,7 +11405,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="121" spans="1:35">
+    <row r="121" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>1191311</v>
       </c>
@@ -11487,7 +11497,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="122" spans="1:35">
+    <row r="122" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>1239230</v>
       </c>
@@ -11576,7 +11586,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="123" spans="1:35">
+    <row r="123" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>1244585</v>
       </c>
@@ -11665,7 +11675,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="124" spans="1:35">
+    <row r="124" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>1252239</v>
       </c>
@@ -11754,7 +11764,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="125" spans="1:35">
+    <row r="125" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>1252612</v>
       </c>
@@ -11840,7 +11850,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="126" spans="1:35">
+    <row r="126" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>1236754</v>
       </c>
@@ -11926,7 +11936,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="127" spans="1:35">
+    <row r="127" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>1236758</v>
       </c>
@@ -12013,15 +12023,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010040E407455DB15F429C332EFB2CC833B9" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6e8ec7461d5261ad0ccdb35c847d66ba">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2a80cc35-9f79-4cbf-a8b4-f259617c00c0" xmlns:ns3="d1cc8434-691a-4797-83e1-dcc9726b69c0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9db85ee8c378c960bff46748ade96960" ns2:_="" ns3:_="">
     <xsd:import namespace="2a80cc35-9f79-4cbf-a8b4-f259617c00c0"/>
@@ -12250,10 +12251,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{940BAA6C-AE74-465B-8418-9E502665F177}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{136F5D4A-747A-4E2C-AFA5-2935924AECAC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2a80cc35-9f79-4cbf-a8b4-f259617c00c0"/>
+    <ds:schemaRef ds:uri="d1cc8434-691a-4797-83e1-dcc9726b69c0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{136F5D4A-747A-4E2C-AFA5-2935924AECAC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{940BAA6C-AE74-465B-8418-9E502665F177}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>